--- a/contacts/contacts.xlsx
+++ b/contacts/contacts.xlsx
@@ -80,10 +80,10 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="42" customWidth="1"/>
+    <col min="13" max="13" width="52" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -153,7 +153,74 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="0">
+        <is>
+          <t>CONTACT-2026-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="0">
+        <is>
+          <t>אבי לוי</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="0">
+        <is>
+          <t>ועד בית</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="0">
+        <is>
+          <t>ORG-2026-001 — בית לחם 49</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="0">
+        <is>
+          <t>חבר ועד בית</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="0">
+        <is>
+          <t>עברית</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="0">
+        <is>
+          <t>Telegram Alexei 2026-07-28</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="0">
+        <is>
+          <t>только после подтверждения</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="0">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="0">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="0">
+        <is>
+          <t>Кейс CASE-2026-001: канализация между домами; они оплатили и хотят разделить цену.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:M2"/>
 </worksheet>
 </file>
--- a/contacts/contacts.xlsx
+++ b/contacts/contacts.xlsx
@@ -220,7 +220,74 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="0">
+        <is>
+          <t>CONTACT-2026-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="0">
+        <is>
+          <t>עאיד אבו סריה</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="0">
+        <is>
+          <t>052-247-3050</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="0">
+        <is>
+          <t>ועד בית</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="0">
+        <is>
+          <t>ORG-2026-001 — בית לחם 49</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="0">
+        <is>
+          <t>יו"ר ועד בית; סוכן ביטוח</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="0">
+        <is>
+          <t>עברית</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="0">
+        <is>
+          <t>Telegram Alexei 2026-08-04; CASE-2026-001</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="0">
+        <is>
+          <t>только после подтверждения</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="0">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr" s="0">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr" s="0">
+        <is>
+          <t>Руководитель домового комитета дома 49; страховой агент. Кейс CASE-2026-001: канализация между домами.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M2"/>
+  <autoFilter ref="A1:M3"/>
 </worksheet>
 </file>